--- a/data/trans_orig/P24E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007 (tasa de respuesta: 98,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,56%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30244</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -958,97 +958,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1760</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5464</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>15,86%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>903</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5996</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4770</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5940</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46660</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>26443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44502</t>
+          <t>44198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>58117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85011</t>
+          <t>85227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>45719</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65846</t>
+          <t>66259</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>30156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48530</t>
+          <t>48630</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>80400</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107389</t>
+          <t>108733</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>23673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35426</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>44270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>46158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74955</t>
+          <t>72998</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48046</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67782</t>
+          <t>67847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>50008</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73426</t>
+          <t>72007</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105584</t>
+          <t>103715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135895</t>
+          <t>134215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28050</t>
+          <t>27882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>48027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28762</t>
+          <t>28737</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>48858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>48524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66620</t>
+          <t>66317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67240</t>
+          <t>65826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90020</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34151</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36114</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34721</t>
+          <t>35062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23062</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>40316</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,27%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>115310</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>155553</t>
+          <t>154693</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>94344</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>219819</t>
+          <t>220511</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>271533</t>
+          <t>268912</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>197991</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>238429</t>
+          <t>237532</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>126402</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>159573</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>332451</t>
+          <t>334467</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>388284</t>
+          <t>386100</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>43792</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>70966</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>85426</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>122082</t>
+          <t>122191</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41875</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>33215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46882</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>64465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84847</t>
+          <t>84357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12521</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>27092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>22595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25519</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44750</t>
+          <t>44595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46155</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70797</t>
+          <t>70222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54817</t>
+          <t>54604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77601</t>
+          <t>77242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107272</t>
+          <t>107192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142345</t>
+          <t>140347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,2%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>57303</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81913</t>
+          <t>81484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>72363</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110245</t>
+          <t>112521</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146117</t>
+          <t>148079</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26842</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39721</t>
+          <t>37998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>43497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67499</t>
+          <t>68227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>40909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63675</t>
+          <t>63601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90469</t>
+          <t>90846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124147</t>
+          <t>123969</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>69597</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95606</t>
+          <t>95006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42719</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65223</t>
+          <t>63882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118805</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153531</t>
+          <t>153907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>25719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27624</t>
+          <t>27600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>50871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34196</t>
+          <t>34620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>58601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34014</t>
+          <t>34686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58144</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74178</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107803</t>
+          <t>110015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63396</t>
+          <t>62919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90155</t>
+          <t>89179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49752</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74709</t>
+          <t>73799</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120910</t>
+          <t>119776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>156305</t>
+          <t>157054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,59%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14417</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35155</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>62668</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>24026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>42539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59180</t>
+          <t>58862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30896</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49065</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13830</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>36746</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58914</t>
+          <t>58670</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22070</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7386,62 +7386,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>5769</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>4646</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11282</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>213993</t>
+          <t>215990</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>266205</t>
+          <t>265488</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>201680</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>246549</t>
+          <t>246045</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>429150</t>
+          <t>428935</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>497431</t>
+          <t>497483</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>271644</t>
+          <t>272930</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>325231</t>
+          <t>325611</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>180332</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>224289</t>
+          <t>226940</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>466350</t>
+          <t>463343</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>534788</t>
+          <t>534896</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>64036</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>103380</t>
+          <t>102087</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>121106</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>171414</t>
+          <t>173376</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016 (tasa de respuesta: 98,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36685</t>
+          <t>36861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53934</t>
+          <t>53552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21825</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18159</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8759,62 +8759,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5182</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>38288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>23178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>46298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73006</t>
+          <t>70816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49366</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68601</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36442</t>
+          <t>37229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55324</t>
+          <t>53741</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91506</t>
+          <t>92082</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118267</t>
+          <t>118086</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,29%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41190</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35026</t>
+          <t>35007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43765</t>
+          <t>43990</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69613</t>
+          <t>71033</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68120</t>
+          <t>68098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90446</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36066</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54198</t>
+          <t>54985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111051</t>
+          <t>109901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139437</t>
+          <t>139971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26305</t>
+          <t>27826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24769</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45595</t>
+          <t>45794</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>32270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>40450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64770</t>
+          <t>65667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>40492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>62302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53183</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74855</t>
+          <t>74452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100485</t>
+          <t>99218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131918</t>
+          <t>131106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32980</t>
+          <t>32520</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55144</t>
+          <t>55210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28670</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49198</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76890</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55450</t>
+          <t>55361</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>40804</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66832</t>
+          <t>66703</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91574</t>
+          <t>91388</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>20691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40940</t>
+          <t>41097</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22307</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12880</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1746</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11269,62 +11269,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>764</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6652</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>111933</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>151632</t>
+          <t>151715</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>105213</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>144340</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>227227</t>
+          <t>228457</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>282473</t>
+          <t>285309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>248920</t>
+          <t>250610</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>295590</t>
+          <t>296246</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>188023</t>
+          <t>188183</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>229106</t>
+          <t>228262</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>450321</t>
+          <t>446226</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>511905</t>
+          <t>508088</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>76988</t>
+          <t>78666</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>113660</t>
+          <t>114770</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>82676</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>138850</t>
+          <t>139632</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>185624</t>
+          <t>186144</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24E-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>22118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38771</t>
+          <t>39215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>26885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46315</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>27342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44198</t>
+          <t>44410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58117</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85227</t>
+          <t>86664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>45576</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>65901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48630</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80400</t>
+          <t>80143</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108733</t>
+          <t>107362</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23673</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36261</t>
+          <t>34533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23708</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44270</t>
+          <t>43395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46158</t>
+          <t>45434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72998</t>
+          <t>73253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67847</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50008</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72007</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103715</t>
+          <t>103883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134215</t>
+          <t>134969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>26943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>24330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25670</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>47541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48524</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66317</t>
+          <t>66327</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>65859</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90574</t>
+          <t>90409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>21287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34025</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>30482</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35062</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23509</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>13751</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>71,35%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>115202</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>154693</t>
+          <t>152688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>91047</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>125986</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>220511</t>
+          <t>217737</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>268912</t>
+          <t>269655</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>196442</t>
+          <t>196836</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>237532</t>
+          <t>238911</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>160085</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>334467</t>
+          <t>333651</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>386100</t>
+          <t>385319</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56523</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>85426</t>
+          <t>83295</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>122191</t>
+          <t>119417</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27380</t>
+          <t>27517</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>41770</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>32448</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>47716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64465</t>
+          <t>63940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84357</t>
+          <t>85903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27092</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25337</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44595</t>
+          <t>45737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46528</t>
+          <t>45575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70222</t>
+          <t>69661</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54604</t>
+          <t>54113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77242</t>
+          <t>77853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107192</t>
+          <t>106844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140347</t>
+          <t>142274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57303</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81484</t>
+          <t>81556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48746</t>
+          <t>48084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72363</t>
+          <t>72023</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112521</t>
+          <t>110471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>148079</t>
+          <t>145877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>27126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37998</t>
+          <t>41256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>43127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68227</t>
+          <t>67868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40909</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63601</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90846</t>
+          <t>88909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>123995</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69597</t>
+          <t>70577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95006</t>
+          <t>96321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42399</t>
+          <t>42756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63882</t>
+          <t>65175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119207</t>
+          <t>118511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153907</t>
+          <t>154700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,12%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25719</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>26963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50871</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34620</t>
+          <t>34472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58601</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34686</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57277</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>74292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110015</t>
+          <t>108635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62919</t>
+          <t>64606</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89179</t>
+          <t>88986</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>47786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73799</t>
+          <t>74672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119776</t>
+          <t>120342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157054</t>
+          <t>156852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16255</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36203</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62668</t>
+          <t>61162</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24026</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42539</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>37848</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58862</t>
+          <t>59705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>30760</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48329</t>
+          <t>49272</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36746</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58670</t>
+          <t>58869</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7437</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>798</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11282</t>
+          <t>11359</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>215990</t>
+          <t>213582</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>265488</t>
+          <t>264725</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>200931</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>246045</t>
+          <t>247267</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>428935</t>
+          <t>430851</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>497483</t>
+          <t>495545</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>272930</t>
+          <t>273722</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>325611</t>
+          <t>326506</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>180426</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>226940</t>
+          <t>225084</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>463343</t>
+          <t>464306</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>534896</t>
+          <t>534862</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>64036</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>101872</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>81211</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>124755</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>173376</t>
+          <t>171650</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -8498,12 +8498,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>16902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>15763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36861</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53552</t>
+          <t>53350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17720</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>19063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35153</t>
+          <t>35865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8954,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38288</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23178</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40530</t>
+          <t>40016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46298</t>
+          <t>47469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70816</t>
+          <t>72938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>49296</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>68911</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37229</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53741</t>
+          <t>54628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92082</t>
+          <t>91173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>117419</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -9180,12 +9180,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9265,12 +9265,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20250</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35007</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43990</t>
+          <t>44354</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71033</t>
+          <t>69785</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9523,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68098</t>
+          <t>66796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90791</t>
+          <t>90265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36237</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54985</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9593,12 +9593,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109901</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139971</t>
+          <t>139452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -9636,12 +9636,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24293</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9671,12 +9671,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>23581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45794</t>
+          <t>45551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -9866,12 +9866,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32270</t>
+          <t>32108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9881,12 +9881,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39488</t>
+          <t>39428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9936,12 +9936,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>39977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65667</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -9979,12 +9979,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40492</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62302</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>52544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74452</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99218</t>
+          <t>98911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131106</t>
+          <t>129466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10064,12 +10064,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -10092,12 +10092,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32520</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47582</t>
+          <t>49779</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76564</t>
+          <t>76190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10322,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25333</t>
+          <t>25268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10337,12 +10337,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10372,12 +10372,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37273</t>
+          <t>37519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -10435,12 +10435,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>37330</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55361</t>
+          <t>56214</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>24318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>39916</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>66703</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91388</t>
+          <t>91640</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>26080</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41097</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10633,12 +10633,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -10778,12 +10778,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>16055</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25190</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10976,12 +10976,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1746</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11417,12 +11417,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13508</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11432,12 +11432,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11475,12 +11475,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>11757</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11545,12 +11545,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>111111</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>151715</t>
+          <t>153223</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11725,12 +11725,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>106998</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>144340</t>
+          <t>143671</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>228457</t>
+          <t>227844</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>285309</t>
+          <t>282334</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -11803,12 +11803,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>250610</t>
+          <t>249457</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>296246</t>
+          <t>296038</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>188183</t>
+          <t>185637</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>228262</t>
+          <t>226477</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>446226</t>
+          <t>449474</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>508088</t>
+          <t>507467</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11888,12 +11888,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>78666</t>
+          <t>77332</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>114770</t>
+          <t>114282</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11966,12 +11966,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11986,12 +11986,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>139632</t>
+          <t>139417</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>186144</t>
+          <t>186232</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12001,12 +12001,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
